--- a/assets/data/excel/events.xlsx
+++ b/assets/data/excel/events.xlsx
@@ -580,11 +580,9 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 5}, {"enemyId": "E002", "level": 6}]</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>[{"enemyId": "E_M001", "level": 5}, {"enemyId": "E_M002", "level": 6}]</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 60}, {"type": "mycelium", "amount": 40}]</t>
@@ -617,11 +615,9 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E011", "level": 8}, {"enemyId": "E012", "level": 8}]</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>[{"enemyId": "E_L001", "level": 8}, {"enemyId": "E_L002", "level": 8}]</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 80}, {"type": "mycelium", "amount": 50}]</t>
@@ -654,11 +650,9 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 10}, {"enemyId": "E004", "level": 11}, {"enemyId": "E005", "level": 12}]</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>[{"enemyId": "E_M003", "level": 10}, {"enemyId": "E_M004", "level": 11}, {"enemyId": "E_M005", "level": 12}]</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 100}, {"type": "mycelium", "amount": 60}]</t>
@@ -691,11 +685,9 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E006", "level": 15}, {"enemyId": "E007", "level": 15}]</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>[{"enemyId": "E_M006", "level": 15}, {"enemyId": "E_M007", "level": 15}]</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 120}, {"type": "mycelium", "amount": 70}]</t>
@@ -728,11 +720,9 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 20}, {"enemyId": "E009", "level": 20}, {"enemyId": "E010", "level": 21}]</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>[{"enemyId": "E_M008", "level": 20}, {"enemyId": "E_M009", "level": 20}, {"enemyId": "E_M010", "level": 21}]</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 150}, {"type": "mycelium", "amount": 90}, {"type": "chip", "amount": 1}]</t>
@@ -765,11 +755,9 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 25}, {"enemyId": "E013", "level": 26}]</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>[{"enemyId": "E_M001", "level": 25}, {"enemyId": "E_L003", "level": 26}]</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 180}, {"type": "mycelium", "amount": 100}]</t>
@@ -802,11 +790,9 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E014", "level": 30}, {"enemyId": "E015", "level": 30}, {"enemyId": "E016", "level": 31}]</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>[{"enemyId": "E_L004", "level": 30}, {"enemyId": "E_L005", "level": 30}, {"enemyId": "E_L006", "level": 31}]</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 220}, {"type": "mycelium", "amount": 120}, {"type": "sourceCore", "amount": 5}]</t>
@@ -839,11 +825,9 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E004", "level": 35}, {"enemyId": "E005", "level": 36}]</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>[{"enemyId": "E_M004", "level": 35}, {"enemyId": "E_M005", "level": 36}]</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 260}, {"type": "mycelium", "amount": 140}]</t>
@@ -876,11 +860,9 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 40}, {"enemyId": "E017", "level": 41}]</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>[{"enemyId": "E_M008", "level": 40}, {"enemyId": "E_L007", "level": 41}]</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 300}, {"type": "mycelium", "amount": 160}, {"type": "chip", "amount": 2}]</t>
@@ -913,11 +895,9 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 50}, {"enemyId": "E018", "level": 50}, {"enemyId": "E019", "level": 51}]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>[{"enemyId": "E_M002", "level": 50}, {"enemyId": "E_L008", "level": 50}, {"enemyId": "E_L009", "level": 51}]</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 350}, {"type": "mycelium", "amount": 180}, {"type": "sourceCore", "amount": 10}]</t>
@@ -950,11 +930,9 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E006", "level": 55}, {"enemyId": "E020", "level": 56}]</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>[{"enemyId": "E_M006", "level": 55}, {"enemyId": "E_L010", "level": 56}]</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 400}, {"type": "mycelium", "amount": 200}]</t>
@@ -987,11 +965,9 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 60}, {"enemyId": "E007", "level": 61}, {"enemyId": "E013", "level": 62}]</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>[{"enemyId": "E_M003", "level": 60}, {"enemyId": "E_M007", "level": 61}, {"enemyId": "E_L003", "level": 62}]</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 450}, {"type": "mycelium", "amount": 220}, {"type": "chip", "amount": 2}]</t>
@@ -1024,11 +1000,9 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 70}, {"enemyId": "E010", "level": 70}]</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>[{"enemyId": "E_M009", "level": 70}, {"enemyId": "E_M010", "level": 70}]</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 500}, {"type": "mycelium", "amount": 250}, {"type": "sourceCore", "amount": 15}]</t>
@@ -1061,11 +1035,9 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E017", "level": 80}, {"enemyId": "E018", "level": 80}, {"enemyId": "E020", "level": 81}]</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>[{"enemyId": "E_L007", "level": 80}, {"enemyId": "E_L008", "level": 80}, {"enemyId": "E_L010", "level": 81}]</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 600}, {"type": "mycelium", "amount": 300}, {"type": "sourceCore", "amount": 20}, {"type": "chip", "amount": 3}]</t>
@@ -1098,11 +1070,9 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E019", "level": 90}, {"enemyId": "E020", "level": 91}]</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>[{"enemyId": "E_L009", "level": 90}, {"enemyId": "E_L010", "level": 91}]</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 700}, {"type": "mycelium", "amount": 350}, {"type": "sourceCore", "amount": 25}, {"type": "shipPart", "amount": 1}]</t>
@@ -1133,13 +1103,11 @@
           <t>在废墟中找到一本泛黄的日志，记录着灾变前最后的日子。</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>日志的最后一页写着：'菌丝扩散速度超出预期，方舟计划必须提前启动。那些被感染的人……他们不再是人类了。我把钥匙藏在实验室第三层的安全柜里。如果你看到这段话，说明一切已经太迟了。'</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 30}, {"type": "mycelium", "amount": 20}]</t>
@@ -1170,13 +1138,11 @@
           <t>一座半毁的通讯塔还在发出微弱的信号，接收器里传来断断续续的声音。</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>信号经过无数次中继，终于拼凑出一段信息：'……方舟……仍在运行……核心温度稳定……等待……回收……坐标……北纬37度……'信号随即中断，只剩下电磁噪声。</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 40}, {"type": "mycelium", "amount": 25}]</t>
@@ -1207,13 +1173,11 @@
           <t>低温保存室里，数十个休眠舱整齐排列，大部分已经破裂。</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>唯一完好的休眠舱上刻着名字：'陈远征——方舟计划首席研究员'。舱内的人已经变成了一团菌丝和血肉的混合物，但他的手中紧握着一个数据芯片。芯片上的标签写着：'菌丝免疫血清——未完成'。</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 50}, {"type": "mycelium", "amount": 30}, {"type": "chip", "amount": 1}]</t>
@@ -1244,13 +1208,11 @@
           <t>一个失心者的尸体旁散落着私人物品——照片、信件、一个孩子的玩具。</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>信件上写着：'小雨，爸爸要去军事基地执行任务，很快就回来。你在家乖乖听妈妈的话，不要出门。外面的空气不好，记得戴面罩。'照片上是一家三口的合影，背景是尚未被菌丝覆盖的城市。</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 35}, {"type": "mycelium", "amount": 20}]</t>
@@ -1281,13 +1243,11 @@
           <t>深入地下设施后，墙壁上的管线突然震动，传来低沉的机械运转声。</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>一个合成语音从扬声器中传出：'方舟核心系统自检完成。当前状态：休眠模式。外部生态评估：不可生存。建议操作：维持休眠。注意：检测到未授权生物信号进入核心区域。安全协议已激活。'走廊尽头的灯依次亮起，通向更深处。</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 60}, {"type": "mycelium", "amount": 40}, {"type": "sourceCore", "amount": 5}]</t>
@@ -1318,8 +1278,6 @@
           <t>一个背着巨大行囊的老人从废墟后走出，摊开一块布，上面摆满了零件和物资。</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>SHOP_WANDERER</t>
@@ -1355,8 +1313,6 @@
           <t>昏暗的地下室里，一个戴着防毒面具的人敲了敲铁门：'要货？先看看你有多少菌丝。'</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>SHOP_BLACKMARKET</t>
@@ -1392,8 +1348,6 @@
           <t>一群拾荒者建立了一个简易交易点，用各种废品换取有用的物资。</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>SHOP_SCAVENGER</t>
@@ -1429,8 +1383,6 @@
           <t>一个仍在运作的自动补给终端，需要军官权限才能访问——或者绕过安全系统。</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>SHOP_MILITARY</t>
@@ -1466,8 +1418,6 @@
           <t>一个全身包裹在菌丝织物中的神秘商人，用源核交换稀有材料。</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>SHOP_MYCELIUM</t>
@@ -1503,9 +1453,6 @@
           <t>探测器捕捉到一个微弱的信号，来源不明，可能是求救，也可能是陷阱。</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 45}, {"type": "mycelium", "amount": 30}]</t>
@@ -1536,9 +1483,6 @@
           <t>前方的空间似乎发生了扭曲，光线弯曲，方向感完全丧失。</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 55}, {"type": "mycelium", "amount": 35}]</t>
@@ -1569,9 +1513,6 @@
           <t>角落里有一个密封的补给箱，外壳上印着方舟计划的标志。</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 40}, {"type": "sourceCore", "amount": 5}]</t>
@@ -1602,9 +1543,6 @@
           <t>脚下的菌丝突然剧烈生长，将整条通道封锁，必须找到出路。</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 50}, {"type": "mycelium", "amount": 60}]</t>
@@ -1635,9 +1573,6 @@
           <t>通讯器收到一段加密广播，解密后似乎是一组坐标和物资投放指令。</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>[{"type": "exp", "amount": 60}, {"type": "mycelium", "amount": 40}, {"type": "chip", "amount": 1}]</t>
